--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97615</v>
+        <v>97618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97618</v>
+        <v>97619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97619</v>
+        <v>97624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136447613</v>
       </c>
       <c r="B4" t="n">
-        <v>41108</v>
+        <v>41110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97624</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
